--- a/artfynd/A 29741-2026 artfynd.xlsx
+++ b/artfynd/A 29741-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ12"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,32 +680,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130798963</v>
+        <v>136886403</v>
       </c>
       <c r="B2" t="n">
-        <v>57141</v>
+        <v>58122</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100090</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nucifraga caryocatactes</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -721,27 +721,23 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillsjön, Vstm</t>
+          <t>Söndagsbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481221</v>
+        <v>481288</v>
       </c>
       <c r="R2" t="n">
-        <v>6596393</v>
+        <v>6596069</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,17 +761,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Spår i snön</t>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,27 +791,27 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Nils Nygren</t>
+          <t>Jim Hellquist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130798963</t>
+          <t>https://artportalen.se/Sighting/136886403</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135506024</v>
+        <v>130798963</v>
       </c>
       <c r="B3" t="n">
-        <v>106310</v>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -818,37 +819,57 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221154</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsstjärna</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lysimachia europaea</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) U. Manns &amp; Anderb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lillsjön, SSO om, Vstm</t>
+          <t>Lillsjön, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481186</v>
+        <v>481221</v>
       </c>
       <c r="R3" t="n">
-        <v>6596385</v>
+        <v>6596393</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,12 +893,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Spår i snön</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,36 +914,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Ruderat, grusyta</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
+          <t>Nils Nygren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135506024</t>
+          <t>https://artportalen.se/Sighting/130798963</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134433703</v>
+        <v>135506024</v>
       </c>
       <c r="B4" t="n">
-        <v>98066</v>
+        <v>106310</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,41 +946,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>221154</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skogsstjärna</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lysimachia europaea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) U. Manns &amp; Anderb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rockesholm, Vstm</t>
+          <t>Lillsjön, SSO om, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481167</v>
+        <v>481186</v>
       </c>
       <c r="R4" t="n">
-        <v>6596341</v>
+        <v>6596385</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,27 +1000,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:53</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:53</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,28 +1016,33 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Ruderat, grusyta</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Owe Nilsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Owe Nilsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134433703</t>
+          <t>https://artportalen.se/Sighting/135506024</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134433704</v>
+        <v>134433703</v>
       </c>
       <c r="B5" t="n">
         <v>98066</v>
@@ -1074,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481132</v>
+        <v>481167</v>
       </c>
       <c r="R5" t="n">
-        <v>6596362</v>
+        <v>6596341</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1109,7 +1116,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,7 +1126,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1150,13 +1157,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134433704</t>
+          <t>https://artportalen.se/Sighting/134433703</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134433706</v>
+        <v>134433704</v>
       </c>
       <c r="B6" t="n">
         <v>98066</v>
@@ -1195,10 +1202,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481138</v>
+        <v>481132</v>
       </c>
       <c r="R6" t="n">
-        <v>6596301</v>
+        <v>6596362</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,7 +1237,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1240,7 +1247,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1271,13 +1278,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134433706</t>
+          <t>https://artportalen.se/Sighting/134433704</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134433707</v>
+        <v>134433706</v>
       </c>
       <c r="B7" t="n">
         <v>98066</v>
@@ -1316,10 +1323,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481133</v>
+        <v>481138</v>
       </c>
       <c r="R7" t="n">
-        <v>6596304</v>
+        <v>6596301</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1392,16 +1399,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134433707</t>
+          <t>https://artportalen.se/Sighting/134433706</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135506022</v>
+        <v>134433707</v>
       </c>
       <c r="B8" t="n">
-        <v>98162</v>
+        <v>98066</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1426,20 +1433,24 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lillsjön, S om, skjutbana, Vstm</t>
+          <t>Rockesholm, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481140</v>
+        <v>481133</v>
       </c>
       <c r="R8" t="n">
-        <v>6596332</v>
+        <v>6596304</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1463,17 +1474,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Längs stigen mot skjutvallen</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,36 +1505,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Hygge</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135506022</t>
+          <t>https://artportalen.se/Sighting/134433707</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134433709</v>
+        <v>135506022</v>
       </c>
       <c r="B9" t="n">
-        <v>98063</v>
+        <v>98162</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1521,16 +1537,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221946</v>
+        <v>221941</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1538,24 +1554,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rockesholm, Vstm</t>
+          <t>Lillsjön, S om, skjutbana, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>481166</v>
+        <v>481140</v>
       </c>
       <c r="R9" t="n">
-        <v>6596345</v>
+        <v>6596332</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1579,27 +1591,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:55</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>10:55</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Längs stigen mot skjutvallen</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1610,28 +1612,33 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Hygge</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Owe Nilsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Owe Nilsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134433709</t>
+          <t>https://artportalen.se/Sighting/135506022</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134433711</v>
+        <v>134433709</v>
       </c>
       <c r="B10" t="n">
         <v>98063</v>
@@ -1670,10 +1677,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>481132</v>
+        <v>481166</v>
       </c>
       <c r="R10" t="n">
-        <v>6596358</v>
+        <v>6596345</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1705,7 +1712,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1715,7 +1722,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1746,13 +1753,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134433711</t>
+          <t>https://artportalen.se/Sighting/134433709</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134433712</v>
+        <v>134433711</v>
       </c>
       <c r="B11" t="n">
         <v>98063</v>
@@ -1791,10 +1798,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>481131</v>
+        <v>481132</v>
       </c>
       <c r="R11" t="n">
-        <v>6596311</v>
+        <v>6596358</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1826,7 +1833,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1836,7 +1843,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1867,16 +1874,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134433712</t>
+          <t>https://artportalen.se/Sighting/134433711</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135506027</v>
+        <v>134433712</v>
       </c>
       <c r="B12" t="n">
-        <v>98160</v>
+        <v>98063</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1884,33 +1891,41 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>224364</v>
+        <v>221946</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lillsjön, SSO om, Vstm</t>
+          <t>Rockesholm, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>481186</v>
+        <v>481131</v>
       </c>
       <c r="R12" t="n">
-        <v>6596385</v>
+        <v>6596311</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1934,12 +1949,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1950,25 +1980,123 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Ruderat, grusyta</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433712</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135506027</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98160</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>224364</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vanlig mattlummer</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lillsjön, SSO om, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>481186</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6596385</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Hällefors</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Grythyttan</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Ruderat, grusyta</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135506027</t>
         </is>
@@ -1987,6 +2115,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29741-2026 artfynd.xlsx
+++ b/artfynd/A 29741-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136886403</v>
       </c>
       <c r="B2" t="n">
-        <v>58122</v>
+        <v>58135</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29741-2026 artfynd.xlsx
+++ b/artfynd/A 29741-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136886403</v>
       </c>
       <c r="B2" t="n">
-        <v>58135</v>
+        <v>58137</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29741-2026 artfynd.xlsx
+++ b/artfynd/A 29741-2026 artfynd.xlsx
@@ -713,17 +713,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>

--- a/artfynd/A 29741-2026 artfynd.xlsx
+++ b/artfynd/A 29741-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136886403</v>
       </c>
       <c r="B2" t="n">
-        <v>58137</v>
+        <v>58147</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29741-2026 artfynd.xlsx
+++ b/artfynd/A 29741-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136886403</v>
       </c>
       <c r="B2" t="n">
-        <v>58147</v>
+        <v>58148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29741-2026 artfynd.xlsx
+++ b/artfynd/A 29741-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136886403</v>
       </c>
       <c r="B2" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 29741-2026 artfynd.xlsx
+++ b/artfynd/A 29741-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136886403</v>
       </c>
       <c r="B2" t="n">
-        <v>58149</v>
+        <v>58152</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
